--- a/artfynd/A 34081-2022 artfynd.xlsx
+++ b/artfynd/A 34081-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34081-2022 artfynd.xlsx
+++ b/artfynd/A 34081-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,69 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96443999</v>
+        <v>63181513</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nyebo 2:3, Sm</t>
+          <t>Ramsås, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584816.0789286011</v>
+        <v>585011</v>
       </c>
       <c r="R2" t="n">
-        <v>6318501.308852299</v>
+        <v>6318571</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,22 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2013-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2013-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +778,763 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Amie Ringberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63200646</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56830</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ramsås, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>585011</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6318571</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>lokal-ID: 8  Box-ID: 8I</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Amie Ringberg, Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128549965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584849</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6318513</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smedmossen solpark NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>63202347</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsås, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>585011</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6318571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-06-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-06-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>lokal-ID: 8  Box-ID: 8I</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Amie Ringberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>63190104</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ramsås, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>585011</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6318571</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-06-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>lokal-ID: 8  Box-ID: 8I</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson, Amie Ringberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96443999</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyebo 2:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584816</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6318501</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Lars Engström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Lars Engström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96444199</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyebo 2:3, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>584818</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6318478</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34081-2022 artfynd.xlsx
+++ b/artfynd/A 34081-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63181513</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63200646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1161,6 +1181,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202347</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1287,6 +1312,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63190104</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1411,6 +1441,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96443999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1535,8 +1570,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96444199</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>